--- a/Outputs/Scenarios/PtX_demand_IE_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_IE_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>1.495982210596268e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001941480072570625</v>
+        <v>0.002111915457780947</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.003235800120951041</v>
+        <v>0.003051779348884794</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>2.15545713815099e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001294320048380416</v>
+        <v>0.001307905435236341</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>2.214619532340416e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01047643320777818</v>
+        <v>0.01139612069498154</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01746072201296362</v>
+        <v>0.01646772633166199</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>1.165589227547588e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>0.00698428880518545</v>
+        <v>0.007057596999283712</v>
       </c>
     </row>
     <row r="43">
